--- a/templates/reports/슬러지반출관리대장.xlsx
+++ b/templates/reports/슬러지반출관리대장.xlsx
@@ -1,35 +1,120 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\AppData\Roaming\Osoo_Handle_App\templates\reports\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDE34F00-C937-48D5-89EF-ACCEF0F86389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="28680" yWindow="-5970" windowWidth="29040" windowHeight="15720" xr2:uid="{0A4F8DB3-B303-4839-8561-6ED3BC43782E}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="템플릿" state="visible" r:id="rId4"/>
+    <sheet name="슬러지반출관리대장" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">슬러지반출관리대장!$A$1:$F$34</definedName>
+    <definedName name="날짜">슬러지반출관리대장!$B$4:$B$34</definedName>
+    <definedName name="대장명">슬러지반출관리대장!$A$1</definedName>
+    <definedName name="비고">슬러지반출관리대장!$F$4:$F$34</definedName>
+    <definedName name="순번">슬러지반출관리대장!$A$4:$A$34</definedName>
+    <definedName name="시간">슬러지반출관리대장!$D$4:$D$34</definedName>
+    <definedName name="업체명">슬러지반출관리대장!$C$4:$C$34</definedName>
+    <definedName name="중량">슬러지반출관리대장!$E$4:$E$34</definedName>
+    <definedName name="현장명">슬러지반출관리대장!$A$2</definedName>
+  </definedNames>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
-    <t>슬러지반출관리대장 기본 템플릿</t>
+    <t>청주(서울)휴게소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>이 파일은 기본 번들 템플릿입니다. 실제 양식은 필요에 따라 교체해주세요.</t>
+    <t>순번</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>날짜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>업체명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시간</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>중량</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026년 3월 슬러지반출 관리대장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
+      <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +125,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,15 +133,55 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -72,9 +197,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -82,44 +207,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -147,14 +272,31 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -182,9 +324,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -193,221 +352,575 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CCF046A-7627-457F-9339-4FF17646B76E}">
+  <dimension ref="A1:F34"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="5.69921875" customWidth="1"/>
+    <col min="2" max="2" width="13.19921875" customWidth="1"/>
+    <col min="3" max="3" width="18.69921875" customWidth="1"/>
+    <col min="4" max="4" width="13.3984375" customWidth="1"/>
+    <col min="5" max="5" width="10.69921875" customWidth="1"/>
+    <col min="6" max="6" width="21.69921875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+    </row>
+    <row r="2" spans="1:6" ht="29.4" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="F2" s="5"/>
+    </row>
+    <row r="3" spans="1:6" s="4" customFormat="1" ht="32.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="B3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A4" s="1">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2">
+        <v>46082</v>
+      </c>
+      <c r="C4" s="1"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A5" s="1">
+        <v>2</v>
+      </c>
+      <c r="B5" s="2">
+        <v>46083</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A6" s="1">
+        <v>3</v>
+      </c>
+      <c r="B6" s="2">
+        <v>46084</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A7" s="1">
+        <v>4</v>
+      </c>
+      <c r="B7" s="2">
+        <v>46085</v>
+      </c>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A8" s="1">
+        <v>5</v>
+      </c>
+      <c r="B8" s="2">
+        <v>46086</v>
+      </c>
+      <c r="C8" s="1"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A9" s="1">
+        <v>6</v>
+      </c>
+      <c r="B9" s="2">
+        <v>46087</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A10" s="1">
+        <v>7</v>
+      </c>
+      <c r="B10" s="2">
+        <v>46088</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A11" s="1">
+        <v>8</v>
+      </c>
+      <c r="B11" s="2">
+        <v>46089</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A12" s="1">
+        <v>9</v>
+      </c>
+      <c r="B12" s="2">
+        <v>46090</v>
+      </c>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A13" s="1">
+        <v>10</v>
+      </c>
+      <c r="B13" s="2">
+        <v>46091</v>
+      </c>
+      <c r="C13" s="1"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A14" s="1">
+        <v>11</v>
+      </c>
+      <c r="B14" s="2">
+        <v>46092</v>
+      </c>
+      <c r="C14" s="1"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A15" s="1">
+        <v>12</v>
+      </c>
+      <c r="B15" s="2">
+        <v>46093</v>
+      </c>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A16" s="1">
+        <v>13</v>
+      </c>
+      <c r="B16" s="2">
+        <v>46094</v>
+      </c>
+      <c r="C16" s="1"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A17" s="1">
+        <v>14</v>
+      </c>
+      <c r="B17" s="2">
+        <v>46095</v>
+      </c>
+      <c r="C17" s="1"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A18" s="1">
+        <v>15</v>
+      </c>
+      <c r="B18" s="2">
+        <v>46096</v>
+      </c>
+      <c r="C18" s="1"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A19" s="1">
+        <v>16</v>
+      </c>
+      <c r="B19" s="2">
+        <v>46097</v>
+      </c>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A20" s="1">
+        <v>17</v>
+      </c>
+      <c r="B20" s="2">
+        <v>46098</v>
+      </c>
+      <c r="C20" s="1"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A21" s="1">
+        <v>18</v>
+      </c>
+      <c r="B21" s="2">
+        <v>46099</v>
+      </c>
+      <c r="C21" s="1"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A22" s="1">
+        <v>19</v>
+      </c>
+      <c r="B22" s="2">
+        <v>46100</v>
+      </c>
+      <c r="C22" s="1"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A23" s="1">
+        <v>20</v>
+      </c>
+      <c r="B23" s="2">
+        <v>46101</v>
+      </c>
+      <c r="C23" s="1"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A24" s="1">
+        <v>21</v>
+      </c>
+      <c r="B24" s="2">
+        <v>46102</v>
+      </c>
+      <c r="C24" s="1"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A25" s="1">
+        <v>22</v>
+      </c>
+      <c r="B25" s="2">
+        <v>46103</v>
+      </c>
+      <c r="C25" s="1"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A26" s="1">
+        <v>23</v>
+      </c>
+      <c r="B26" s="2">
+        <v>46104</v>
+      </c>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A27" s="1">
+        <v>24</v>
+      </c>
+      <c r="B27" s="2">
+        <v>46105</v>
+      </c>
+      <c r="C27" s="1"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A28" s="1">
+        <v>25</v>
+      </c>
+      <c r="B28" s="2">
+        <v>46106</v>
+      </c>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A29" s="1">
+        <v>26</v>
+      </c>
+      <c r="B29" s="2">
+        <v>46107</v>
+      </c>
+      <c r="C29" s="1"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A30" s="1">
+        <v>27</v>
+      </c>
+      <c r="B30" s="2">
+        <v>46108</v>
+      </c>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A31" s="1">
+        <v>28</v>
+      </c>
+      <c r="B31" s="2">
+        <v>46109</v>
+      </c>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A32" s="1">
+        <v>29</v>
+      </c>
+      <c r="B32" s="2">
+        <v>46110</v>
+      </c>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A33" s="1">
+        <v>30</v>
+      </c>
+      <c r="B33" s="2">
+        <v>46111</v>
+      </c>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A34" s="1">
+        <v>31</v>
+      </c>
+      <c r="B34" s="2">
+        <v>46112</v>
+      </c>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.62" right="0.44" top="1.39" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="34" max="5" man="1"/>
+  </rowBreaks>
 </worksheet>
 </file>